--- a/exports/skills-overview.xlsx
+++ b/exports/skills-overview.xlsx
@@ -58,7 +58,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L10"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -573,60 +573,122 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">地脈尖刺</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">earthspike_line</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">主動</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ground_line</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">地面依序冒出尖刺，形成直線封鎖區，適合卡窄道與打衝臉怪群。</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">沿玩家前方地面依序竄出尖刺，形成直線封路與延遲爆發，擅長壓制衝臉怪與窄道敵群。</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">適合卡窄道、打直線怪群、阻擋近身壓力。和傷害強化、攻速提升很搭，後期餘震與終段爆發更強。</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傷害 3 | 冷卻 3.76 秒 | 射程 220 | 尖刺段數 4 | 地脈寬度 58 | 推進間隔 0.19 秒 | 尖刺持續 0.36 秒</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傷害 3 | 冷卻 3.64 秒 | 射程 250 | 尖刺段數 5 | 地脈寬度 60 | 推進間隔 0.18 秒 | 尖刺持續 0.37 秒</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傷害 4 | 冷卻 3.5 秒 | 射程 270 | 尖刺段數 5 | 地脈寬度 66 | 推進間隔 0.17 秒 | 尖刺持續 0.38 秒</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傷害 4 | 冷卻 3.38 秒 | 射程 290 | 尖刺段數 6 | 地脈寬度 68 | 推進間隔 0.17 秒 | 尖刺持續 0.4 秒 | 餘震 0.32 秒 | 餘震倍率 55%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">傷害 6 | 冷卻 3.26 秒 | 射程 340 | 尖刺段數 7 | 地脈寬度 72 | 推進間隔 0.16 秒 | 尖刺持續 0.42 秒 | 餘震 0.3 秒 | 餘震倍率 65% | 終段爆發</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">新星綻放</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">nova_bloom</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">主動</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">explosive</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">拋出會爆炸的種子，造成範圍傷害。</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">拋物式爆炸種子，節奏較慢但單發範圍與爆發都高，適合補重擊與範圍清場。</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">適合爆發、守群聚、補足大範圍 AoE。和傷害強化、攻速提升、投射增幅很搭。</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">傷害 3 | 冷卻 2.1 秒 | 射程 300 | 投射物 1 | 爆炸半徑 60</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">傷害 4 | 冷卻 1.92 秒 | 射程 320 | 投射物 1 | 爆炸半徑 70</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">傷害 4 | 冷卻 1.76 秒 | 投射物 2 | 爆炸半徑 78</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">傷害 5 | 冷卻 1.56 秒 | 投射物 2 | 爆炸半徑 90</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">傷害 7 | 冷卻 1.36 秒 | 投射物 3 | 爆炸半徑 104</t>
         </is>
